--- a/学员导入模板.xlsx
+++ b/学员导入模板.xlsx
@@ -448,14 +448,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="35" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -481,6 +482,11 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>所属班级</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>状态</t>
         </is>
       </c>
@@ -508,6 +514,11 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
+          <t>2026年川庆钻井队电气技能提升班（第一期）</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
           <t>活跃</t>
         </is>
       </c>
@@ -535,6 +546,11 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
+          <t>2026年川庆钻井队电气技能提升班（第一期）</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
           <t>活跃</t>
         </is>
       </c>
@@ -560,7 +576,8 @@
           <t>电气安全</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr"/>
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>活跃</t>
         </is>
